--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118741766</v>
+        <v>118741876</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>94513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388048</v>
+        <v>388047</v>
       </c>
       <c r="R2" t="n">
-        <v>6611026</v>
+        <v>6611039</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118741876</v>
+        <v>118741766</v>
       </c>
       <c r="B3" t="n">
-        <v>94513</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388047</v>
+        <v>388048</v>
       </c>
       <c r="R3" t="n">
-        <v>6611039</v>
+        <v>6611026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118741876</v>
+        <v>118741858</v>
       </c>
       <c r="B2" t="n">
-        <v>94513</v>
+        <v>95394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -761,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -888,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118741858</v>
+        <v>118741876</v>
       </c>
       <c r="B4" t="n">
-        <v>95394</v>
+        <v>94513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +920,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,26 +994,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118741858</v>
+        <v>118741876</v>
       </c>
       <c r="B2" t="n">
-        <v>95394</v>
+        <v>94520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -761,26 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118741766</v>
+        <v>118741858</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>95401</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,47 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388048</v>
+        <v>388047</v>
       </c>
       <c r="R3" t="n">
-        <v>6611026</v>
+        <v>6611039</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,6 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118741876</v>
+        <v>118741766</v>
       </c>
       <c r="B4" t="n">
-        <v>94513</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388047</v>
+        <v>388048</v>
       </c>
       <c r="R4" t="n">
-        <v>6611039</v>
+        <v>6611026</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118741858</v>
+        <v>118741766</v>
       </c>
       <c r="B3" t="n">
-        <v>95401</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388047</v>
+        <v>388048</v>
       </c>
       <c r="R3" t="n">
-        <v>6611039</v>
+        <v>6611026</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,26 +872,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118741766</v>
+        <v>118741858</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>95401</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +900,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kusdrågen (Kusdrågen), Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388048</v>
+        <v>388047</v>
       </c>
       <c r="R4" t="n">
-        <v>6611026</v>
+        <v>6611039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,6 +974,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>121344584</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>121344584</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>121344584</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>121344584</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>121344584</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>121344584</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>121344584</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,1191 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125684788</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79988</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>388041</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6611000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125684866</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>388049</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6611024</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125684886</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>388050</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6611036</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125684783</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>388042</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6611029</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stockbergen, färska hack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125684789</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79932</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>388038</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6610996</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125684782</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>388042</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611028</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125684776</v>
+      </c>
+      <c r="B12" t="n">
+        <v>95766</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>388039</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6611037</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125684780</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>388040</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6611035</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125684786</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79932</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>388045</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6611009</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125684787</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80063</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>388040</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6611002</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125684784</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>388045</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6611028</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1133,12 +1133,7 @@
         <v>125684788</v>
       </c>
       <c r="B6" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,37 +1232,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125684866</v>
+        <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95820</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388049</v>
+        <v>388039</v>
       </c>
       <c r="R7" t="n">
-        <v>6611024</v>
+        <v>6611037</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1307,12 +1297,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1344,37 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684886</v>
+        <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388050</v>
+        <v>388040</v>
       </c>
       <c r="R8" t="n">
-        <v>6611036</v>
+        <v>6611035</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1414,12 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1451,37 +1436,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684783</v>
+        <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388042</v>
+        <v>388049</v>
       </c>
       <c r="R9" t="n">
-        <v>6611029</v>
+        <v>6611024</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1521,17 +1501,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Stockbergen, färska hack</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,37 +1538,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125684789</v>
+        <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388038</v>
+        <v>388050</v>
       </c>
       <c r="R10" t="n">
-        <v>6610996</v>
+        <v>6611036</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1628,12 +1603,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1665,15 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125684782</v>
+        <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,7 +1670,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>141</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1709,7 +1679,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388042</v>
+        <v>388045</v>
       </c>
       <c r="R11" t="n">
         <v>6611028</v>
@@ -1776,15 +1746,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684776</v>
+        <v>125684787</v>
       </c>
       <c r="B12" t="n">
-        <v>95766</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,21 +1757,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388039</v>
+        <v>388040</v>
       </c>
       <c r="R12" t="n">
-        <v>6611037</v>
+        <v>6611002</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1846,12 +1811,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1883,15 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125684780</v>
+        <v>125684783</v>
       </c>
       <c r="B13" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1923,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388040</v>
+        <v>388042</v>
       </c>
       <c r="R13" t="n">
-        <v>6611035</v>
+        <v>6611029</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1963,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,50 +1950,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125684786</v>
+        <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388045</v>
+        <v>388042</v>
       </c>
       <c r="R14" t="n">
-        <v>6611009</v>
+        <v>6611028</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2097,15 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125684787</v>
+        <v>125684786</v>
       </c>
       <c r="B15" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2113,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2137,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388040</v>
+        <v>388045</v>
       </c>
       <c r="R15" t="n">
-        <v>6611002</v>
+        <v>6611009</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2204,54 +2158,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684784</v>
+        <v>125684789</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388045</v>
+        <v>388038</v>
       </c>
       <c r="R16" t="n">
-        <v>6611028</v>
+        <v>6610996</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95820</v>
+        <v>95827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1133,7 +1133,7 @@
         <v>125684788</v>
       </c>
       <c r="B6" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95827</v>
+        <v>95830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125684787</v>
       </c>
       <c r="B12" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>125684786</v>
       </c>
       <c r="B15" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>125684789</v>
       </c>
       <c r="B16" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1133,7 +1133,7 @@
         <v>125684788</v>
       </c>
       <c r="B6" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95830</v>
+        <v>95834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>125684787</v>
       </c>
       <c r="B12" t="n">
-        <v>80106</v>
+        <v>80110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>125684786</v>
       </c>
       <c r="B15" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>125684789</v>
       </c>
       <c r="B16" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95834</v>
+        <v>95835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684787</v>
+        <v>125684783</v>
       </c>
       <c r="B12" t="n">
-        <v>80110</v>
+        <v>57648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388040</v>
+        <v>388042</v>
       </c>
       <c r="R12" t="n">
-        <v>6611002</v>
+        <v>6611029</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, färska hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125684783</v>
+        <v>125684787</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>80110</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388042</v>
+        <v>388040</v>
       </c>
       <c r="R13" t="n">
-        <v>6611029</v>
+        <v>6611002</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stockbergen, färska hack</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1133,7 +1133,7 @@
         <v>125684788</v>
       </c>
       <c r="B6" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95835</v>
+        <v>95837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684783</v>
+        <v>125684787</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>80111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388042</v>
+        <v>388040</v>
       </c>
       <c r="R12" t="n">
-        <v>6611029</v>
+        <v>6611002</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stockbergen, färska hack</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125684787</v>
+        <v>125684783</v>
       </c>
       <c r="B13" t="n">
-        <v>80110</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388040</v>
+        <v>388042</v>
       </c>
       <c r="R13" t="n">
-        <v>6611002</v>
+        <v>6611029</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>125684786</v>
       </c>
       <c r="B15" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>125684789</v>
       </c>
       <c r="B16" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95837</v>
+        <v>95839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684787</v>
+        <v>125684783</v>
       </c>
       <c r="B12" t="n">
-        <v>80111</v>
+        <v>57649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388040</v>
+        <v>388042</v>
       </c>
       <c r="R12" t="n">
-        <v>6611002</v>
+        <v>6611029</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, färska hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125684783</v>
+        <v>125684787</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>80111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388042</v>
+        <v>388040</v>
       </c>
       <c r="R13" t="n">
-        <v>6611029</v>
+        <v>6611002</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stockbergen, färska hack</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95839</v>
+        <v>95841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1133,7 +1133,7 @@
         <v>125684788</v>
       </c>
       <c r="B6" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95841</v>
+        <v>95845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,32 +1746,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684783</v>
+        <v>125684787</v>
       </c>
       <c r="B12" t="n">
-        <v>57649</v>
+        <v>80115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388042</v>
+        <v>388040</v>
       </c>
       <c r="R12" t="n">
-        <v>6611029</v>
+        <v>6611002</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stockbergen, färska hack</t>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125684787</v>
+        <v>125684783</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388040</v>
+        <v>388042</v>
       </c>
       <c r="R13" t="n">
-        <v>6611002</v>
+        <v>6611029</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, färska hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>125684786</v>
       </c>
       <c r="B15" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>125684789</v>
       </c>
       <c r="B16" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1334,32 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684780</v>
+        <v>125684866</v>
       </c>
       <c r="B8" t="n">
-        <v>96602</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388040</v>
+        <v>388049</v>
       </c>
       <c r="R8" t="n">
-        <v>6611035</v>
+        <v>6611024</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1436,32 +1436,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684866</v>
+        <v>125684780</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>96602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388049</v>
+        <v>388040</v>
       </c>
       <c r="R9" t="n">
-        <v>6611024</v>
+        <v>6611035</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -1235,7 +1235,7 @@
         <v>125684776</v>
       </c>
       <c r="B7" t="n">
-        <v>95845</v>
+        <v>95848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,32 +1334,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684866</v>
+        <v>125684780</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>96605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388049</v>
+        <v>388040</v>
       </c>
       <c r="R8" t="n">
-        <v>6611024</v>
+        <v>6611035</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1436,32 +1436,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684780</v>
+        <v>125684866</v>
       </c>
       <c r="B9" t="n">
-        <v>96602</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388040</v>
+        <v>388049</v>
       </c>
       <c r="R9" t="n">
-        <v>6611035</v>
+        <v>6611024</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1541,7 +1541,7 @@
         <v>125684886</v>
       </c>
       <c r="B10" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>125684784</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>125684782</v>
       </c>
       <c r="B14" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23086-2024 artfynd.xlsx
+++ b/artfynd/A 23086-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>118741858</v>
       </c>
       <c r="B2" t="n">
-        <v>95406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -797,62 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118741766</v>
+        <v>125684780</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388048</v>
+        <v>388040</v>
       </c>
       <c r="R3" t="n">
-        <v>6611026</v>
+        <v>6611035</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,12 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,62 +882,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118741876</v>
+        <v>123699630</v>
       </c>
       <c r="B4" t="n">
-        <v>94525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kusdrågen (Kusdrågen), Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388047</v>
+        <v>387952</v>
       </c>
       <c r="R4" t="n">
-        <v>6611039</v>
+        <v>6611071</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,71 +979,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121344584</v>
+        <v>118741876</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kusdrågen, SSV om, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>388047</v>
       </c>
       <c r="R5" t="n">
-        <v>6611026</v>
+        <v>6611039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,11 +1054,6 @@
           <t>Brunskog</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>S-Arv-0849</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2024-07-28</t>
@@ -1114,7 +1076,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1122,18 +1084,14 @@
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125684788</v>
+        <v>125684776</v>
       </c>
       <c r="B6" t="n">
-        <v>80040</v>
+        <v>96601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388041</v>
+        <v>388039</v>
       </c>
       <c r="R6" t="n">
-        <v>6611000</v>
+        <v>6611037</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1232,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125684776</v>
+        <v>125684894</v>
       </c>
       <c r="B7" t="n">
-        <v>95848</v>
+        <v>95957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>2383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bågpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Plagiomnium medium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388039</v>
+        <v>387925</v>
       </c>
       <c r="R7" t="n">
-        <v>6611037</v>
+        <v>6611069</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1334,48 +1292,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684780</v>
+        <v>118335253</v>
       </c>
       <c r="B8" t="n">
-        <v>96605</v>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Kusdrågen, Arvika, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388040</v>
+        <v>387991</v>
       </c>
       <c r="R8" t="n">
-        <v>6611035</v>
+        <v>6611130</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,17 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,44 +1377,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684866</v>
+        <v>125684786</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1471,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388049</v>
+        <v>388045</v>
       </c>
       <c r="R9" t="n">
-        <v>6611024</v>
+        <v>6611009</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,12 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1538,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125684886</v>
+        <v>125684789</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388050</v>
+        <v>388038</v>
       </c>
       <c r="R10" t="n">
-        <v>6611036</v>
+        <v>6610996</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,12 +1556,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1640,49 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125684784</v>
+        <v>125684787</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388045</v>
+        <v>388040</v>
       </c>
       <c r="R11" t="n">
-        <v>6611028</v>
+        <v>6611002</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1746,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125684787</v>
+        <v>125684783</v>
       </c>
       <c r="B12" t="n">
-        <v>80115</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1781,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388040</v>
+        <v>388042</v>
       </c>
       <c r="R12" t="n">
-        <v>6611002</v>
+        <v>6611029</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1821,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stockbergen</t>
+          <t>Stockbergen, färska hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,48 +1797,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125684783</v>
+        <v>66538370</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Stockbergen-Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388042</v>
+        <v>388063</v>
       </c>
       <c r="R13" t="n">
-        <v>6611029</v>
+        <v>6611066</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,17 +1862,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2012-05-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2012-05-19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Stockbergen, färska hack</t>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,26 +1883,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>21190</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125684782</v>
+        <v>118741766</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,22 +1934,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388042</v>
+        <v>388048</v>
       </c>
       <c r="R14" t="n">
-        <v>6611028</v>
+        <v>6611026</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,17 +1978,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,60 +1998,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125684786</v>
+        <v>121344584</v>
       </c>
       <c r="B15" t="n">
-        <v>79984</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Kusdrågen, SSV om, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388045</v>
+        <v>388047</v>
       </c>
       <c r="R15" t="n">
-        <v>6611009</v>
+        <v>6611026</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2119,19 +2082,19 @@
           <t>Brunskog</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>S-Arv-0849</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,57 +2109,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125684789</v>
+        <v>125684782</v>
       </c>
       <c r="B16" t="n">
-        <v>79984</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388038</v>
+        <v>388042</v>
       </c>
       <c r="R16" t="n">
-        <v>6610996</v>
+        <v>6611028</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2257,6 +2228,622 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125684784</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>388045</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6611028</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125684865</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>388044</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6611152</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125684866</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>388049</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6611024</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125684886</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>388050</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6611036</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125684790</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>387961</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6610980</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125684788</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>388041</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6611000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
